--- a/ProyectoTamañoAngularAparente/DatosTiempo.xlsx
+++ b/ProyectoTamañoAngularAparente/DatosTiempo.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielvillada/Documents/IntroduccionAstronomiaPractica/ProyectoTamañoAngularAparente/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielvillada/Documents/IntroduccionAstronomiaPractica/ProyectoTamañoAngularAparente/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A588F39-39BE-E649-9264-0938404A14BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC3B708-2764-5848-B4B9-ECFBFAACBF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14540" xr2:uid="{6D95BC64-B0CE-CD41-A373-DACA3CFB6784}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="12800" windowHeight="14540" xr2:uid="{6D95BC64-B0CE-CD41-A373-DACA3CFB6784}"/>
   </bookViews>
   <sheets>
     <sheet name="Sol" sheetId="1" r:id="rId1"/>
-    <sheet name="Luna" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
-  <si>
-    <t>Hora</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Tiempo</t>
   </si>
@@ -78,8 +74,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,33 +391,192 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53BD49E-FAC8-A84F-BB0B-D4AA1EA7CE80}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C7DA82-4B14-5F4F-9B99-000876C80407}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <f>6+32/60</f>
+        <v>6.5333333333333332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <f>5+20/60</f>
+        <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <f>6+48/60</f>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <f>4+11/60</f>
+        <v>4.1833333333333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <f>4+10/60</f>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <f>3+45/60</f>
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f>4+16/60</f>
+        <v>4.2666666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <f>3+50/60</f>
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f>3+20/60</f>
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>4+30/60</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>2833833</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>3050433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>2500750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>2333550</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>3166700</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>1667417</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>2250567</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>2750200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>2967050</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>3050933</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>2400200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>2733900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>2731845</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>2564210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>3048975</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>2889430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>2412765</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>2976520</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>2658390</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>2801275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>3122640</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>2337580</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>2915860</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>2743195</v>
       </c>
     </row>
   </sheetData>
